--- a/microcode.xlsx
+++ b/microcode.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10119"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10811"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/elizabethhong/Downloads/CS 2110/Spring 2025/HW-LC3Datapath/student/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aalajlan6/Documents/School documents/2110/hw03/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE8A9769-4C5D-9649-9D8C-C98002731DBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51157DEC-D0BF-2245-BE95-B34714F11633}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17280" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16520" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="microcode" sheetId="1" r:id="rId1"/>
@@ -5939,32 +5939,72 @@
         <v>90</v>
       </c>
       <c r="B71" s="76"/>
-      <c r="C71" s="79"/>
-      <c r="D71" s="79"/>
-      <c r="E71" s="79"/>
-      <c r="F71" s="79"/>
-      <c r="G71" s="79"/>
-      <c r="H71" s="80"/>
-      <c r="I71" s="81"/>
-      <c r="J71" s="81"/>
-      <c r="K71" s="81"/>
-      <c r="L71" s="81"/>
-      <c r="M71" s="82"/>
-      <c r="N71" s="83"/>
+      <c r="C71" s="79">
+        <v>0</v>
+      </c>
+      <c r="D71" s="79">
+        <v>0</v>
+      </c>
+      <c r="E71" s="79">
+        <v>0</v>
+      </c>
+      <c r="F71" s="79">
+        <v>0</v>
+      </c>
+      <c r="G71" s="79">
+        <v>0</v>
+      </c>
+      <c r="H71" s="80">
+        <v>1</v>
+      </c>
+      <c r="I71" s="81">
+        <v>0</v>
+      </c>
+      <c r="J71" s="81">
+        <v>0</v>
+      </c>
+      <c r="K71" s="81">
+        <v>1</v>
+      </c>
+      <c r="L71" s="81">
+        <v>0</v>
+      </c>
+      <c r="M71" s="82">
+        <v>1</v>
+      </c>
+      <c r="N71" s="83">
+        <v>0</v>
+      </c>
       <c r="O71" s="82">
         <v>0</v>
       </c>
       <c r="P71" s="84">
         <v>1</v>
       </c>
-      <c r="Q71" s="82"/>
-      <c r="R71" s="85"/>
-      <c r="S71" s="82"/>
-      <c r="T71" s="85"/>
-      <c r="U71" s="85"/>
-      <c r="V71" s="83"/>
-      <c r="W71" s="86"/>
-      <c r="X71" s="86"/>
+      <c r="Q71" s="82">
+        <v>0</v>
+      </c>
+      <c r="R71" s="85">
+        <v>0</v>
+      </c>
+      <c r="S71" s="82">
+        <v>0</v>
+      </c>
+      <c r="T71" s="85">
+        <v>0</v>
+      </c>
+      <c r="U71" s="85">
+        <v>0</v>
+      </c>
+      <c r="V71" s="83">
+        <v>0</v>
+      </c>
+      <c r="W71" s="86">
+        <v>0</v>
+      </c>
+      <c r="X71" s="86">
+        <v>0</v>
+      </c>
       <c r="Y71" s="110">
         <v>1</v>
       </c>
@@ -5985,7 +6025,7 @@
       </c>
       <c r="AH71" t="str">
         <f>_xlfn.CONCAT(BIN2HEX(_xlfn.CONCAT(C71:F71), 1), BIN2HEX(_xlfn.CONCAT(G71:N71), 2), BIN2HEX(_xlfn.CONCAT(O71:V71), 2), BIN2HEX(_xlfn.CONCAT(W71:AD71), 2) )</f>
-        <v>0000125</v>
+        <v>04A4025</v>
       </c>
     </row>
     <row r="72" spans="1:34" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -5993,32 +6033,72 @@
         <v>91</v>
       </c>
       <c r="B72" s="76"/>
-      <c r="C72" s="79"/>
-      <c r="D72" s="79"/>
-      <c r="E72" s="79"/>
-      <c r="F72" s="79"/>
-      <c r="G72" s="79"/>
-      <c r="H72" s="80"/>
-      <c r="I72" s="81"/>
-      <c r="J72" s="81"/>
-      <c r="K72" s="81"/>
-      <c r="L72" s="81"/>
-      <c r="M72" s="82"/>
-      <c r="N72" s="83"/>
+      <c r="C72" s="79">
+        <v>0</v>
+      </c>
+      <c r="D72" s="79">
+        <v>0</v>
+      </c>
+      <c r="E72" s="79">
+        <v>0</v>
+      </c>
+      <c r="F72" s="79">
+        <v>0</v>
+      </c>
+      <c r="G72" s="79">
+        <v>0</v>
+      </c>
+      <c r="H72" s="80">
+        <v>1</v>
+      </c>
+      <c r="I72" s="81">
+        <v>0</v>
+      </c>
+      <c r="J72" s="81">
+        <v>0</v>
+      </c>
+      <c r="K72" s="81">
+        <v>0</v>
+      </c>
+      <c r="L72" s="81">
+        <v>0</v>
+      </c>
+      <c r="M72" s="82">
+        <v>0</v>
+      </c>
+      <c r="N72" s="83">
+        <v>0</v>
+      </c>
       <c r="O72" s="82">
         <v>0</v>
       </c>
       <c r="P72" s="84">
         <v>0</v>
       </c>
-      <c r="Q72" s="82"/>
-      <c r="R72" s="85"/>
-      <c r="S72" s="82"/>
-      <c r="T72" s="85"/>
-      <c r="U72" s="85"/>
-      <c r="V72" s="83"/>
-      <c r="W72" s="86"/>
-      <c r="X72" s="86"/>
+      <c r="Q72" s="82">
+        <v>0</v>
+      </c>
+      <c r="R72" s="85">
+        <v>0</v>
+      </c>
+      <c r="S72" s="82">
+        <v>0</v>
+      </c>
+      <c r="T72" s="85">
+        <v>0</v>
+      </c>
+      <c r="U72" s="85">
+        <v>0</v>
+      </c>
+      <c r="V72" s="83">
+        <v>0</v>
+      </c>
+      <c r="W72" s="86">
+        <v>0</v>
+      </c>
+      <c r="X72" s="86">
+        <v>0</v>
+      </c>
       <c r="Y72" s="110">
         <v>1</v>
       </c>
@@ -6039,7 +6119,7 @@
       </c>
       <c r="AH72" t="str">
         <f t="shared" ref="AH72:AH75" si="5">_xlfn.CONCAT(BIN2HEX(_xlfn.CONCAT(C72:F72), 1), BIN2HEX(_xlfn.CONCAT(G72:N72), 2), BIN2HEX(_xlfn.CONCAT(O72:V72), 2), BIN2HEX(_xlfn.CONCAT(W72:AD72), 2) )</f>
-        <v>0000026</v>
+        <v>0400026</v>
       </c>
     </row>
     <row r="73" spans="1:34" x14ac:dyDescent="0.2">
@@ -6047,32 +6127,72 @@
         <v>92</v>
       </c>
       <c r="B73" s="76"/>
-      <c r="C73" s="79"/>
-      <c r="D73" s="79"/>
-      <c r="E73" s="79"/>
-      <c r="F73" s="79"/>
-      <c r="G73" s="79"/>
-      <c r="H73" s="80"/>
-      <c r="I73" s="81"/>
-      <c r="J73" s="81"/>
-      <c r="K73" s="81"/>
-      <c r="L73" s="81"/>
-      <c r="M73" s="82"/>
-      <c r="N73" s="83"/>
+      <c r="C73" s="79">
+        <v>1</v>
+      </c>
+      <c r="D73" s="79">
+        <v>0</v>
+      </c>
+      <c r="E73" s="79">
+        <v>0</v>
+      </c>
+      <c r="F73" s="79">
+        <v>0</v>
+      </c>
+      <c r="G73" s="79">
+        <v>0</v>
+      </c>
+      <c r="H73" s="80">
+        <v>0</v>
+      </c>
+      <c r="I73" s="81">
+        <v>1</v>
+      </c>
+      <c r="J73" s="81">
+        <v>0</v>
+      </c>
+      <c r="K73" s="81">
+        <v>0</v>
+      </c>
+      <c r="L73" s="81">
+        <v>0</v>
+      </c>
+      <c r="M73" s="82">
+        <v>0</v>
+      </c>
+      <c r="N73" s="83">
+        <v>0</v>
+      </c>
       <c r="O73" s="82">
         <v>0</v>
       </c>
       <c r="P73" s="84">
         <v>0</v>
       </c>
-      <c r="Q73" s="82"/>
-      <c r="R73" s="85"/>
-      <c r="S73" s="82"/>
-      <c r="T73" s="85"/>
-      <c r="U73" s="85"/>
-      <c r="V73" s="83"/>
-      <c r="W73" s="86"/>
-      <c r="X73" s="86"/>
+      <c r="Q73" s="82">
+        <v>0</v>
+      </c>
+      <c r="R73" s="85">
+        <v>0</v>
+      </c>
+      <c r="S73" s="82">
+        <v>0</v>
+      </c>
+      <c r="T73" s="85">
+        <v>0</v>
+      </c>
+      <c r="U73" s="85">
+        <v>0</v>
+      </c>
+      <c r="V73" s="83">
+        <v>0</v>
+      </c>
+      <c r="W73" s="86">
+        <v>0</v>
+      </c>
+      <c r="X73" s="86">
+        <v>0</v>
+      </c>
       <c r="Y73" s="110">
         <v>1</v>
       </c>
@@ -6093,7 +6213,7 @@
       </c>
       <c r="AH73" t="str">
         <f t="shared" si="5"/>
-        <v>0000027</v>
+        <v>8200027</v>
       </c>
     </row>
     <row r="74" spans="1:34" x14ac:dyDescent="0.2">
@@ -6101,32 +6221,72 @@
         <v>93</v>
       </c>
       <c r="B74" s="76"/>
-      <c r="C74" s="79"/>
-      <c r="D74" s="79"/>
-      <c r="E74" s="79"/>
-      <c r="F74" s="79"/>
-      <c r="G74" s="79"/>
-      <c r="H74" s="80"/>
-      <c r="I74" s="81"/>
-      <c r="J74" s="81"/>
-      <c r="K74" s="81"/>
-      <c r="L74" s="81"/>
-      <c r="M74" s="82"/>
-      <c r="N74" s="83"/>
+      <c r="C74" s="79">
+        <v>0</v>
+      </c>
+      <c r="D74" s="79">
+        <v>1</v>
+      </c>
+      <c r="E74" s="79">
+        <v>0</v>
+      </c>
+      <c r="F74" s="79">
+        <v>0</v>
+      </c>
+      <c r="G74" s="79">
+        <v>0</v>
+      </c>
+      <c r="H74" s="80">
+        <v>0</v>
+      </c>
+      <c r="I74" s="81">
+        <v>0</v>
+      </c>
+      <c r="J74" s="81">
+        <v>0</v>
+      </c>
+      <c r="K74" s="81">
+        <v>0</v>
+      </c>
+      <c r="L74" s="81">
+        <v>0</v>
+      </c>
+      <c r="M74" s="82">
+        <v>0</v>
+      </c>
+      <c r="N74" s="83">
+        <v>0</v>
+      </c>
       <c r="O74" s="82">
         <v>0</v>
       </c>
       <c r="P74" s="84">
         <v>0</v>
       </c>
-      <c r="Q74" s="82"/>
-      <c r="R74" s="85"/>
-      <c r="S74" s="82"/>
-      <c r="T74" s="85"/>
-      <c r="U74" s="85"/>
-      <c r="V74" s="83"/>
-      <c r="W74" s="86"/>
-      <c r="X74" s="86"/>
+      <c r="Q74" s="82">
+        <v>0</v>
+      </c>
+      <c r="R74" s="85">
+        <v>0</v>
+      </c>
+      <c r="S74" s="82">
+        <v>0</v>
+      </c>
+      <c r="T74" s="85">
+        <v>0</v>
+      </c>
+      <c r="U74" s="85">
+        <v>0</v>
+      </c>
+      <c r="V74" s="83">
+        <v>0</v>
+      </c>
+      <c r="W74" s="86">
+        <v>1</v>
+      </c>
+      <c r="X74" s="86">
+        <v>0</v>
+      </c>
       <c r="Y74" s="110">
         <v>1</v>
       </c>
@@ -6147,7 +6307,7 @@
       </c>
       <c r="AH74" t="str">
         <f t="shared" si="5"/>
-        <v>0000028</v>
+        <v>40000A8</v>
       </c>
     </row>
     <row r="75" spans="1:34" x14ac:dyDescent="0.2">
@@ -6155,32 +6315,72 @@
         <v>94</v>
       </c>
       <c r="B75" s="76"/>
-      <c r="C75" s="87"/>
-      <c r="D75" s="88"/>
-      <c r="E75" s="88"/>
-      <c r="F75" s="88"/>
-      <c r="G75" s="88"/>
-      <c r="H75" s="88"/>
-      <c r="I75" s="89"/>
-      <c r="J75" s="89"/>
-      <c r="K75" s="89"/>
-      <c r="L75" s="89"/>
-      <c r="M75" s="90"/>
-      <c r="N75" s="91"/>
+      <c r="C75" s="87">
+        <v>0</v>
+      </c>
+      <c r="D75" s="88">
+        <v>0</v>
+      </c>
+      <c r="E75" s="88">
+        <v>0</v>
+      </c>
+      <c r="F75" s="88">
+        <v>0</v>
+      </c>
+      <c r="G75" s="88">
+        <v>0</v>
+      </c>
+      <c r="H75" s="88">
+        <v>1</v>
+      </c>
+      <c r="I75" s="89">
+        <v>0</v>
+      </c>
+      <c r="J75" s="89">
+        <v>1</v>
+      </c>
+      <c r="K75" s="89">
+        <v>0</v>
+      </c>
+      <c r="L75" s="89">
+        <v>0</v>
+      </c>
+      <c r="M75" s="90">
+        <v>1</v>
+      </c>
+      <c r="N75" s="91">
+        <v>0</v>
+      </c>
       <c r="O75" s="91">
         <v>0</v>
       </c>
       <c r="P75" s="91">
         <v>0</v>
       </c>
-      <c r="Q75" s="91"/>
-      <c r="R75" s="90"/>
-      <c r="S75" s="91"/>
-      <c r="T75" s="91"/>
-      <c r="U75" s="90"/>
-      <c r="V75" s="91"/>
-      <c r="W75" s="92"/>
-      <c r="X75" s="92"/>
+      <c r="Q75" s="91">
+        <v>0</v>
+      </c>
+      <c r="R75" s="90">
+        <v>0</v>
+      </c>
+      <c r="S75" s="91">
+        <v>0</v>
+      </c>
+      <c r="T75" s="91">
+        <v>0</v>
+      </c>
+      <c r="U75" s="90">
+        <v>0</v>
+      </c>
+      <c r="V75" s="91">
+        <v>0</v>
+      </c>
+      <c r="W75" s="92">
+        <v>0</v>
+      </c>
+      <c r="X75" s="92">
+        <v>0</v>
+      </c>
       <c r="Y75" s="116">
         <v>1</v>
       </c>
@@ -6201,7 +6401,7 @@
       </c>
       <c r="AH75" t="str">
         <f t="shared" si="5"/>
-        <v>000003F</v>
+        <v>052003F</v>
       </c>
     </row>
     <row r="76" spans="1:34" ht="31" x14ac:dyDescent="0.35">
@@ -7149,7 +7349,7 @@
       </c>
       <c r="D9" s="63" t="str">
         <f>IFERROR(VLOOKUP(C9,microcode!A$5:AH$90, 34, FALSE), 0)</f>
-        <v>0000125</v>
+        <v>04A4025</v>
       </c>
       <c r="E9" t="s">
         <v>87</v>
@@ -7623,7 +7823,7 @@
       </c>
       <c r="D38" s="63" t="str">
         <f>IFERROR(VLOOKUP(C38,microcode!A$5:AH$90, 34, FALSE), 0)</f>
-        <v>0000026</v>
+        <v>0400026</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.2">
@@ -7639,7 +7839,7 @@
       </c>
       <c r="D39" s="63" t="str">
         <f>IFERROR(VLOOKUP(C39,microcode!A$5:AH$90, 34, FALSE), 0)</f>
-        <v>0000027</v>
+        <v>8200027</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.2">
@@ -7655,7 +7855,7 @@
       </c>
       <c r="D40" s="63" t="str">
         <f>IFERROR(VLOOKUP(C40,microcode!A$5:AH$90, 34, FALSE), 0)</f>
-        <v>0000028</v>
+        <v>40000A8</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.2">
@@ -7671,7 +7871,7 @@
       </c>
       <c r="D41" s="63" t="str">
         <f>IFERROR(VLOOKUP(C41,microcode!A$5:AH$90, 34, FALSE), 0)</f>
-        <v>000003F</v>
+        <v>052003F</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.2">

--- a/microcode.xlsx
+++ b/microcode.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aalajlan6/Documents/School documents/2110/hw03/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51157DEC-D0BF-2245-BE95-B34714F11633}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92B4905B-4900-3C43-AB6D-4462FE9F695F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16520" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5375,30 +5375,66 @@
         <v>76</v>
       </c>
       <c r="B59" s="38"/>
-      <c r="C59" s="87"/>
-      <c r="D59" s="88"/>
-      <c r="E59" s="88"/>
-      <c r="F59" s="88"/>
-      <c r="G59" s="88"/>
-      <c r="H59" s="88"/>
-      <c r="I59" s="89"/>
-      <c r="J59" s="89"/>
-      <c r="K59" s="89"/>
-      <c r="L59" s="89"/>
-      <c r="M59" s="90"/>
-      <c r="N59" s="91"/>
+      <c r="C59" s="87">
+        <v>0</v>
+      </c>
+      <c r="D59" s="88">
+        <v>0</v>
+      </c>
+      <c r="E59" s="88">
+        <v>0</v>
+      </c>
+      <c r="F59" s="88">
+        <v>0</v>
+      </c>
+      <c r="G59" s="88">
+        <v>0</v>
+      </c>
+      <c r="H59" s="88">
+        <v>1</v>
+      </c>
+      <c r="I59" s="89">
+        <v>0</v>
+      </c>
+      <c r="J59" s="89">
+        <v>0</v>
+      </c>
+      <c r="K59" s="89">
+        <v>0</v>
+      </c>
+      <c r="L59" s="89">
+        <v>0</v>
+      </c>
+      <c r="M59" s="90">
+        <v>0</v>
+      </c>
+      <c r="N59" s="91">
+        <v>1</v>
+      </c>
       <c r="O59" s="91">
         <v>0</v>
       </c>
       <c r="P59" s="83">
         <v>0</v>
       </c>
-      <c r="Q59" s="91"/>
-      <c r="R59" s="90"/>
-      <c r="S59" s="91"/>
-      <c r="T59" s="91"/>
-      <c r="U59" s="90"/>
-      <c r="V59" s="91"/>
+      <c r="Q59" s="91">
+        <v>0</v>
+      </c>
+      <c r="R59" s="90">
+        <v>1</v>
+      </c>
+      <c r="S59" s="91">
+        <v>0</v>
+      </c>
+      <c r="T59" s="91">
+        <v>0</v>
+      </c>
+      <c r="U59" s="90">
+        <v>0</v>
+      </c>
+      <c r="V59" s="91">
+        <v>0</v>
+      </c>
       <c r="W59" s="92"/>
       <c r="X59" s="92"/>
       <c r="Y59" s="117">
@@ -5421,7 +5457,7 @@
       </c>
       <c r="AH59" t="str">
         <f>_xlfn.CONCAT(BIN2HEX(_xlfn.CONCAT(C59:F59), 1), BIN2HEX(_xlfn.CONCAT(G59:N59), 2), BIN2HEX(_xlfn.CONCAT(O59:V59), 2), BIN2HEX(_xlfn.CONCAT(W59:AD59), 2) )</f>
-        <v>000003F</v>
+        <v>041103F</v>
       </c>
     </row>
     <row r="60" spans="1:34" ht="31" x14ac:dyDescent="0.35">
@@ -7419,7 +7455,7 @@
       </c>
       <c r="D13" s="63" t="str">
         <f>IFERROR(VLOOKUP(C13,microcode!A$5:AH$90, 34, FALSE), 0)</f>
-        <v>000003F</v>
+        <v>041103F</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">

--- a/microcode.xlsx
+++ b/microcode.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aalajlan6/Documents/School documents/2110/hw03/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92B4905B-4900-3C43-AB6D-4462FE9F695F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E8F225B-845F-5845-BD8E-357FE746EA6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16520" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5531,32 +5531,72 @@
         <v>78</v>
       </c>
       <c r="B62" s="76"/>
-      <c r="C62" s="93"/>
-      <c r="D62" s="94"/>
-      <c r="E62" s="94"/>
-      <c r="F62" s="94"/>
-      <c r="G62" s="94"/>
-      <c r="H62" s="94"/>
-      <c r="I62" s="95"/>
-      <c r="J62" s="95"/>
-      <c r="K62" s="95"/>
-      <c r="L62" s="95"/>
-      <c r="M62" s="82"/>
-      <c r="N62" s="83"/>
+      <c r="C62" s="93">
+        <v>1</v>
+      </c>
+      <c r="D62" s="94">
+        <v>0</v>
+      </c>
+      <c r="E62" s="94">
+        <v>0</v>
+      </c>
+      <c r="F62" s="94">
+        <v>0</v>
+      </c>
+      <c r="G62" s="94">
+        <v>0</v>
+      </c>
+      <c r="H62" s="94">
+        <v>0</v>
+      </c>
+      <c r="I62" s="95">
+        <v>0</v>
+      </c>
+      <c r="J62" s="95">
+        <v>0</v>
+      </c>
+      <c r="K62" s="95">
+        <v>0</v>
+      </c>
+      <c r="L62" s="95">
+        <v>1</v>
+      </c>
+      <c r="M62" s="82">
+        <v>0</v>
+      </c>
+      <c r="N62" s="83">
+        <v>0</v>
+      </c>
       <c r="O62" s="83">
         <v>0</v>
       </c>
       <c r="P62" s="83">
         <v>1</v>
       </c>
-      <c r="Q62" s="83"/>
-      <c r="R62" s="82"/>
-      <c r="S62" s="83"/>
-      <c r="T62" s="83"/>
-      <c r="U62" s="82"/>
-      <c r="V62" s="83"/>
-      <c r="W62" s="96"/>
-      <c r="X62" s="96"/>
+      <c r="Q62" s="83">
+        <v>1</v>
+      </c>
+      <c r="R62" s="82">
+        <v>0</v>
+      </c>
+      <c r="S62" s="83">
+        <v>1</v>
+      </c>
+      <c r="T62" s="83">
+        <v>1</v>
+      </c>
+      <c r="U62" s="82">
+        <v>0</v>
+      </c>
+      <c r="V62" s="83">
+        <v>0</v>
+      </c>
+      <c r="W62" s="96">
+        <v>0</v>
+      </c>
+      <c r="X62" s="96">
+        <v>0</v>
+      </c>
       <c r="Y62" s="110">
         <v>1</v>
       </c>
@@ -5577,7 +5617,7 @@
       </c>
       <c r="AH62" t="str">
         <f t="shared" ref="AH62:AH68" si="4">_xlfn.CONCAT(BIN2HEX(_xlfn.CONCAT(C62:F62), 1), BIN2HEX(_xlfn.CONCAT(G62:N62), 2), BIN2HEX(_xlfn.CONCAT(O62:V62), 2), BIN2HEX(_xlfn.CONCAT(W62:AD62), 2) )</f>
-        <v>0000129</v>
+        <v>8046C29</v>
       </c>
     </row>
     <row r="63" spans="1:34" x14ac:dyDescent="0.2">
@@ -5585,32 +5625,72 @@
         <v>79</v>
       </c>
       <c r="B63" s="76"/>
-      <c r="C63" s="93"/>
-      <c r="D63" s="94"/>
-      <c r="E63" s="94"/>
-      <c r="F63" s="94"/>
-      <c r="G63" s="94"/>
-      <c r="H63" s="94"/>
-      <c r="I63" s="95"/>
-      <c r="J63" s="95"/>
-      <c r="K63" s="95"/>
-      <c r="L63" s="95"/>
-      <c r="M63" s="82"/>
-      <c r="N63" s="83"/>
+      <c r="C63" s="93">
+        <v>0</v>
+      </c>
+      <c r="D63" s="94">
+        <v>1</v>
+      </c>
+      <c r="E63" s="94">
+        <v>0</v>
+      </c>
+      <c r="F63" s="94">
+        <v>0</v>
+      </c>
+      <c r="G63" s="94">
+        <v>0</v>
+      </c>
+      <c r="H63" s="94">
+        <v>0</v>
+      </c>
+      <c r="I63" s="95">
+        <v>0</v>
+      </c>
+      <c r="J63" s="95">
+        <v>0</v>
+      </c>
+      <c r="K63" s="95">
+        <v>0</v>
+      </c>
+      <c r="L63" s="95">
+        <v>0</v>
+      </c>
+      <c r="M63" s="82">
+        <v>0</v>
+      </c>
+      <c r="N63" s="83">
+        <v>0</v>
+      </c>
       <c r="O63" s="83">
         <v>0</v>
       </c>
       <c r="P63" s="83">
         <v>0</v>
       </c>
-      <c r="Q63" s="83"/>
-      <c r="R63" s="82"/>
-      <c r="S63" s="83"/>
-      <c r="T63" s="83"/>
-      <c r="U63" s="82"/>
-      <c r="V63" s="83"/>
-      <c r="W63" s="96"/>
-      <c r="X63" s="96"/>
+      <c r="Q63" s="83">
+        <v>0</v>
+      </c>
+      <c r="R63" s="82">
+        <v>0</v>
+      </c>
+      <c r="S63" s="83">
+        <v>0</v>
+      </c>
+      <c r="T63" s="83">
+        <v>0</v>
+      </c>
+      <c r="U63" s="82">
+        <v>0</v>
+      </c>
+      <c r="V63" s="83">
+        <v>0</v>
+      </c>
+      <c r="W63" s="96">
+        <v>1</v>
+      </c>
+      <c r="X63" s="96">
+        <v>0</v>
+      </c>
       <c r="Y63" s="110">
         <v>1</v>
       </c>
@@ -5631,7 +5711,7 @@
       </c>
       <c r="AH63" t="str">
         <f t="shared" si="4"/>
-        <v>000002A</v>
+        <v>40000AA</v>
       </c>
     </row>
     <row r="64" spans="1:34" x14ac:dyDescent="0.2">
@@ -5639,32 +5719,72 @@
         <v>80</v>
       </c>
       <c r="B64" s="76"/>
-      <c r="C64" s="93"/>
-      <c r="D64" s="94"/>
-      <c r="E64" s="94"/>
-      <c r="F64" s="94"/>
-      <c r="G64" s="94"/>
-      <c r="H64" s="94"/>
-      <c r="I64" s="95"/>
-      <c r="J64" s="95"/>
-      <c r="K64" s="95"/>
-      <c r="L64" s="95"/>
-      <c r="M64" s="82"/>
-      <c r="N64" s="83"/>
+      <c r="C64" s="93">
+        <v>1</v>
+      </c>
+      <c r="D64" s="94">
+        <v>0</v>
+      </c>
+      <c r="E64" s="94">
+        <v>0</v>
+      </c>
+      <c r="F64" s="94">
+        <v>0</v>
+      </c>
+      <c r="G64" s="94">
+        <v>0</v>
+      </c>
+      <c r="H64" s="94">
+        <v>0</v>
+      </c>
+      <c r="I64" s="95">
+        <v>0</v>
+      </c>
+      <c r="J64" s="95">
+        <v>1</v>
+      </c>
+      <c r="K64" s="95">
+        <v>0</v>
+      </c>
+      <c r="L64" s="95">
+        <v>0</v>
+      </c>
+      <c r="M64" s="82">
+        <v>0</v>
+      </c>
+      <c r="N64" s="83">
+        <v>0</v>
+      </c>
       <c r="O64" s="83">
         <v>0</v>
       </c>
       <c r="P64" s="83">
         <v>0</v>
       </c>
-      <c r="Q64" s="83"/>
-      <c r="R64" s="82"/>
-      <c r="S64" s="83"/>
-      <c r="T64" s="83"/>
-      <c r="U64" s="82"/>
-      <c r="V64" s="83"/>
-      <c r="W64" s="96"/>
-      <c r="X64" s="96"/>
+      <c r="Q64" s="83">
+        <v>0</v>
+      </c>
+      <c r="R64" s="82">
+        <v>0</v>
+      </c>
+      <c r="S64" s="83">
+        <v>0</v>
+      </c>
+      <c r="T64" s="83">
+        <v>0</v>
+      </c>
+      <c r="U64" s="82">
+        <v>0</v>
+      </c>
+      <c r="V64" s="83">
+        <v>0</v>
+      </c>
+      <c r="W64" s="96">
+        <v>0</v>
+      </c>
+      <c r="X64" s="96">
+        <v>0</v>
+      </c>
       <c r="Y64" s="110">
         <v>1</v>
       </c>
@@ -5685,7 +5805,7 @@
       </c>
       <c r="AH64" t="str">
         <f t="shared" si="4"/>
-        <v>000002B</v>
+        <v>810002B</v>
       </c>
     </row>
     <row r="65" spans="1:34" x14ac:dyDescent="0.2">
@@ -5693,32 +5813,72 @@
         <v>81</v>
       </c>
       <c r="B65" s="130"/>
-      <c r="C65" s="93"/>
-      <c r="D65" s="93"/>
-      <c r="E65" s="93"/>
-      <c r="F65" s="93"/>
-      <c r="G65" s="93"/>
-      <c r="H65" s="93"/>
-      <c r="I65" s="81"/>
-      <c r="J65" s="81"/>
-      <c r="K65" s="81"/>
-      <c r="L65" s="81"/>
-      <c r="M65" s="85"/>
-      <c r="N65" s="83"/>
+      <c r="C65" s="93">
+        <v>0</v>
+      </c>
+      <c r="D65" s="93">
+        <v>1</v>
+      </c>
+      <c r="E65" s="93">
+        <v>0</v>
+      </c>
+      <c r="F65" s="93">
+        <v>0</v>
+      </c>
+      <c r="G65" s="93">
+        <v>0</v>
+      </c>
+      <c r="H65" s="93">
+        <v>0</v>
+      </c>
+      <c r="I65" s="81">
+        <v>0</v>
+      </c>
+      <c r="J65" s="81">
+        <v>0</v>
+      </c>
+      <c r="K65" s="81">
+        <v>0</v>
+      </c>
+      <c r="L65" s="81">
+        <v>0</v>
+      </c>
+      <c r="M65" s="85">
+        <v>0</v>
+      </c>
+      <c r="N65" s="83">
+        <v>0</v>
+      </c>
       <c r="O65" s="84">
         <v>0</v>
       </c>
       <c r="P65" s="84">
         <v>0</v>
       </c>
-      <c r="Q65" s="84"/>
-      <c r="R65" s="85"/>
-      <c r="S65" s="83"/>
-      <c r="T65" s="84"/>
-      <c r="U65" s="85"/>
-      <c r="V65" s="83"/>
-      <c r="W65" s="109"/>
-      <c r="X65" s="109"/>
+      <c r="Q65" s="84">
+        <v>0</v>
+      </c>
+      <c r="R65" s="85">
+        <v>0</v>
+      </c>
+      <c r="S65" s="83">
+        <v>0</v>
+      </c>
+      <c r="T65" s="84">
+        <v>0</v>
+      </c>
+      <c r="U65" s="85">
+        <v>0</v>
+      </c>
+      <c r="V65" s="83">
+        <v>0</v>
+      </c>
+      <c r="W65" s="109">
+        <v>1</v>
+      </c>
+      <c r="X65" s="109">
+        <v>0</v>
+      </c>
       <c r="Y65" s="97">
         <v>1</v>
       </c>
@@ -5739,7 +5899,7 @@
       </c>
       <c r="AH65" t="str">
         <f t="shared" si="4"/>
-        <v>000002C</v>
+        <v>40000AC</v>
       </c>
     </row>
     <row r="66" spans="1:34" x14ac:dyDescent="0.2">
@@ -5747,32 +5907,72 @@
         <v>82</v>
       </c>
       <c r="B66" s="76"/>
-      <c r="C66" s="93"/>
-      <c r="D66" s="94"/>
-      <c r="E66" s="94"/>
-      <c r="F66" s="94"/>
-      <c r="G66" s="94"/>
-      <c r="H66" s="94"/>
-      <c r="I66" s="95"/>
-      <c r="J66" s="95"/>
-      <c r="K66" s="95"/>
-      <c r="L66" s="95"/>
-      <c r="M66" s="82"/>
-      <c r="N66" s="83"/>
+      <c r="C66" s="93">
+        <v>1</v>
+      </c>
+      <c r="D66" s="94">
+        <v>0</v>
+      </c>
+      <c r="E66" s="94">
+        <v>0</v>
+      </c>
+      <c r="F66" s="94">
+        <v>0</v>
+      </c>
+      <c r="G66" s="94">
+        <v>0</v>
+      </c>
+      <c r="H66" s="94">
+        <v>0</v>
+      </c>
+      <c r="I66" s="95">
+        <v>0</v>
+      </c>
+      <c r="J66" s="95">
+        <v>1</v>
+      </c>
+      <c r="K66" s="95">
+        <v>0</v>
+      </c>
+      <c r="L66" s="95">
+        <v>0</v>
+      </c>
+      <c r="M66" s="82">
+        <v>0</v>
+      </c>
+      <c r="N66" s="83">
+        <v>0</v>
+      </c>
       <c r="O66" s="83">
         <v>0</v>
       </c>
       <c r="P66" s="83">
         <v>0</v>
       </c>
-      <c r="Q66" s="83"/>
-      <c r="R66" s="82"/>
-      <c r="S66" s="83"/>
-      <c r="T66" s="83"/>
-      <c r="U66" s="82"/>
-      <c r="V66" s="83"/>
-      <c r="W66" s="96"/>
-      <c r="X66" s="126"/>
+      <c r="Q66" s="83">
+        <v>0</v>
+      </c>
+      <c r="R66" s="82">
+        <v>0</v>
+      </c>
+      <c r="S66" s="83">
+        <v>0</v>
+      </c>
+      <c r="T66" s="83">
+        <v>0</v>
+      </c>
+      <c r="U66" s="82">
+        <v>0</v>
+      </c>
+      <c r="V66" s="83">
+        <v>0</v>
+      </c>
+      <c r="W66" s="96">
+        <v>0</v>
+      </c>
+      <c r="X66" s="126">
+        <v>0</v>
+      </c>
       <c r="Y66" s="97">
         <v>1</v>
       </c>
@@ -5793,7 +5993,7 @@
       </c>
       <c r="AH66" t="str">
         <f t="shared" si="4"/>
-        <v>000002D</v>
+        <v>810002D</v>
       </c>
     </row>
     <row r="67" spans="1:34" x14ac:dyDescent="0.2">
@@ -5801,32 +6001,72 @@
         <v>83</v>
       </c>
       <c r="B67" s="76"/>
-      <c r="C67" s="93"/>
-      <c r="D67" s="94"/>
-      <c r="E67" s="94"/>
-      <c r="F67" s="94"/>
-      <c r="G67" s="94"/>
-      <c r="H67" s="94"/>
-      <c r="I67" s="95"/>
-      <c r="J67" s="95"/>
-      <c r="K67" s="95"/>
-      <c r="L67" s="95"/>
-      <c r="M67" s="82"/>
-      <c r="N67" s="83"/>
+      <c r="C67" s="93">
+        <v>0</v>
+      </c>
+      <c r="D67" s="94">
+        <v>1</v>
+      </c>
+      <c r="E67" s="94">
+        <v>0</v>
+      </c>
+      <c r="F67" s="94">
+        <v>0</v>
+      </c>
+      <c r="G67" s="94">
+        <v>0</v>
+      </c>
+      <c r="H67" s="94">
+        <v>0</v>
+      </c>
+      <c r="I67" s="95">
+        <v>0</v>
+      </c>
+      <c r="J67" s="95">
+        <v>0</v>
+      </c>
+      <c r="K67" s="95">
+        <v>1</v>
+      </c>
+      <c r="L67" s="95">
+        <v>0</v>
+      </c>
+      <c r="M67" s="82">
+        <v>0</v>
+      </c>
+      <c r="N67" s="83">
+        <v>0</v>
+      </c>
       <c r="O67" s="83">
         <v>0</v>
       </c>
       <c r="P67" s="83">
         <v>0</v>
       </c>
-      <c r="Q67" s="83"/>
-      <c r="R67" s="82"/>
-      <c r="S67" s="83"/>
-      <c r="T67" s="83"/>
-      <c r="U67" s="82"/>
-      <c r="V67" s="83"/>
-      <c r="W67" s="96"/>
-      <c r="X67" s="126"/>
+      <c r="Q67" s="83">
+        <v>0</v>
+      </c>
+      <c r="R67" s="82">
+        <v>0</v>
+      </c>
+      <c r="S67" s="83">
+        <v>0</v>
+      </c>
+      <c r="T67" s="83">
+        <v>0</v>
+      </c>
+      <c r="U67" s="82">
+        <v>1</v>
+      </c>
+      <c r="V67" s="83">
+        <v>1</v>
+      </c>
+      <c r="W67" s="96">
+        <v>0</v>
+      </c>
+      <c r="X67" s="126">
+        <v>0</v>
+      </c>
       <c r="Y67" s="97">
         <v>1</v>
       </c>
@@ -5847,7 +6087,7 @@
       </c>
       <c r="AH67" t="str">
         <f t="shared" si="4"/>
-        <v>000002E</v>
+        <v>408032E</v>
       </c>
     </row>
     <row r="68" spans="1:34" x14ac:dyDescent="0.2">
@@ -5855,32 +6095,72 @@
         <v>84</v>
       </c>
       <c r="B68" s="76"/>
-      <c r="C68" s="93"/>
-      <c r="D68" s="94"/>
-      <c r="E68" s="94"/>
-      <c r="F68" s="94"/>
-      <c r="G68" s="94"/>
-      <c r="H68" s="94"/>
-      <c r="I68" s="95"/>
-      <c r="J68" s="95"/>
-      <c r="K68" s="95"/>
-      <c r="L68" s="95"/>
-      <c r="M68" s="82"/>
-      <c r="N68" s="83"/>
+      <c r="C68" s="93">
+        <v>0</v>
+      </c>
+      <c r="D68" s="94">
+        <v>0</v>
+      </c>
+      <c r="E68" s="94">
+        <v>0</v>
+      </c>
+      <c r="F68" s="94">
+        <v>0</v>
+      </c>
+      <c r="G68" s="94">
+        <v>0</v>
+      </c>
+      <c r="H68" s="94">
+        <v>0</v>
+      </c>
+      <c r="I68" s="95">
+        <v>0</v>
+      </c>
+      <c r="J68" s="95">
+        <v>0</v>
+      </c>
+      <c r="K68" s="95">
+        <v>0</v>
+      </c>
+      <c r="L68" s="95">
+        <v>0</v>
+      </c>
+      <c r="M68" s="82">
+        <v>0</v>
+      </c>
+      <c r="N68" s="83">
+        <v>0</v>
+      </c>
       <c r="O68" s="83">
         <v>0</v>
       </c>
       <c r="P68" s="83">
         <v>0</v>
       </c>
-      <c r="Q68" s="83"/>
-      <c r="R68" s="82"/>
-      <c r="S68" s="83"/>
-      <c r="T68" s="83"/>
-      <c r="U68" s="82"/>
-      <c r="V68" s="83"/>
-      <c r="W68" s="96"/>
-      <c r="X68" s="126"/>
+      <c r="Q68" s="83">
+        <v>0</v>
+      </c>
+      <c r="R68" s="82">
+        <v>0</v>
+      </c>
+      <c r="S68" s="83">
+        <v>0</v>
+      </c>
+      <c r="T68" s="83">
+        <v>0</v>
+      </c>
+      <c r="U68" s="82">
+        <v>0</v>
+      </c>
+      <c r="V68" s="83">
+        <v>0</v>
+      </c>
+      <c r="W68" s="96">
+        <v>1</v>
+      </c>
+      <c r="X68" s="126">
+        <v>1</v>
+      </c>
       <c r="Y68" s="97">
         <v>1</v>
       </c>
@@ -5901,7 +6181,7 @@
       </c>
       <c r="AH68" t="str">
         <f t="shared" si="4"/>
-        <v>000003F</v>
+        <v>00000FF</v>
       </c>
     </row>
     <row r="69" spans="1:34" ht="31" x14ac:dyDescent="0.35">
@@ -7471,7 +7751,7 @@
       </c>
       <c r="D14" s="63" t="str">
         <f>IFERROR(VLOOKUP(C14,microcode!A$5:AH$90, 34, FALSE), 0)</f>
-        <v>0000129</v>
+        <v>8046C29</v>
       </c>
       <c r="E14" t="s">
         <v>88</v>
@@ -7923,7 +8203,7 @@
       </c>
       <c r="D42" s="63" t="str">
         <f>IFERROR(VLOOKUP(C42,microcode!A$5:AH$90, 34, FALSE), 0)</f>
-        <v>000002A</v>
+        <v>40000AA</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.2">
@@ -7939,7 +8219,7 @@
       </c>
       <c r="D43" s="63" t="str">
         <f>IFERROR(VLOOKUP(C43,microcode!A$5:AH$90, 34, FALSE), 0)</f>
-        <v>000002B</v>
+        <v>810002B</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.2">
@@ -7955,7 +8235,7 @@
       </c>
       <c r="D44" s="63" t="str">
         <f>IFERROR(VLOOKUP(C44,microcode!A$5:AH$90, 34, FALSE), 0)</f>
-        <v>000002C</v>
+        <v>40000AC</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.2">
@@ -7971,7 +8251,7 @@
       </c>
       <c r="D45" s="63" t="str">
         <f>IFERROR(VLOOKUP(C45,microcode!A$5:AH$90, 34, FALSE), 0)</f>
-        <v>000002D</v>
+        <v>810002D</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.2">
@@ -7987,7 +8267,7 @@
       </c>
       <c r="D46" s="63" t="str">
         <f>IFERROR(VLOOKUP(C46,microcode!A$5:AH$90, 34, FALSE), 0)</f>
-        <v>000002E</v>
+        <v>408032E</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.2">
@@ -8003,7 +8283,7 @@
       </c>
       <c r="D47" s="63" t="str">
         <f>IFERROR(VLOOKUP(C47,microcode!A$5:AH$90, 34, FALSE), 0)</f>
-        <v>000003F</v>
+        <v>00000FF</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.2">
